--- a/processed_ruby_restored_xlsx/sc032d_３日目：みるく.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032d_３日目：みるく.ss.xlsx
@@ -548,8 +548,8 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>She's honest and can't lie, so if she realizes she has
-it she'll probably return it.</t>
+          <t>She's honest and can't lie, so if she realizes she
+has it she'll probably return it.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -808,8 +808,8 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Well, if she's somewhere in the dorm I'll run into her
-eventually, but it'd be bad to meet someone else
+          <t>Well, if she's somewhere in the dorm I'll run into
+her eventually, but it'd be bad to meet someone else
 first.</t>
         </is>
       </c>
@@ -1130,7 +1130,8 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Up until that point I’d vaguely imagined those things.</t>
+          <t>Up until that point I’d vaguely imagined those
+things.</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1176,8 +1177,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>And on top of that, she’s using my electric toothbrush
-to stimulate her between her legs…</t>
+          <t>And on top of that, she’s using my electric
+toothbrush to stimulate her between her legs…</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1271,8 +1272,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Her expression is tense, but not painfully so, and yet
-as if melting...</t>
+          <t>Her expression is tense, but not painfully so, and
+yet as if melting...</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1519,7 +1520,8 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Did the toothbrush hit a really good spot by accident？</t>
+          <t>Did the toothbrush hit a really good spot by
+accident？</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1595,8 +1597,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Is this the first time she's becoming aware of feeling
-pleasure...？</t>
+          <t>Is this the first time she's becoming aware of
+feeling pleasure...？</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1829,8 +1831,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>She seems to be gradually figuring out the good spots,
-but it's still a mysterious feeling to her.</t>
+          <t>She seems to be gradually figuring out the good
+spots, but it's still a mysterious feeling to her.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,7 +1877,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>She kept pressing the good spot and startling herself.</t>
+          <t>She kept pressing the good spot and startling
+herself.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -2091,8 +2094,8 @@
       <c r="B106" s="1" t="inlineStr">
         <is>
           <t>...I want to teach her, but maybe this is something
-she has to experience and internalize herself by doing
-it many times.</t>
+she has to experience and internalize herself by
+doing it many times.</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2122,7 +2125,8 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>If you try, the more you try the better it'll feel...！</t>
+          <t>If you try, the more you try the better it'll
+feel...！</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2198,8 +2202,9 @@
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>But since she's starting to realize it feels good, she
-ends up moving the toothbrush toward between her legs.</t>
+          <t>But since she's starting to realize it feels good,
+she ends up moving the toothbrush toward between her
+legs.</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2427,9 +2432,9 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>No sooner had I thought that, Miru-chan began pressing
-the toothbrush against her between (my/her) legs
-again.</t>
+          <t>No sooner had I thought that, Miru-chan began
+pressing the toothbrush against her between (my/her)
+legs again.</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2474,9 +2479,9 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>With the toothbrush against her between (my/her) legs,
-Miru-chan trembled as she desperately stifled her
-voice.</t>
+          <t>With the toothbrush against her between (my/her)
+legs, Miru-chan trembled as she desperately stifled
+her voice.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2673,8 +2678,8 @@
       <c r="B144" s="1" t="inlineStr">
         <is>
           <t>...Miru-chan stared off for a bit, then suddenly
-flustered, headed for the sink and started rinsing her
-toothbrush with water.</t>
+flustered, headed for the sink and started rinsing
+her toothbrush with water.</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2919,7 +2924,8 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>I almost got caught peeking at Miru-chan masturbating.</t>
+          <t>I almost got caught peeking at Miru-chan
+masturbating.</t>
         </is>
       </c>
       <c r="C160" t="n">

--- a/processed_ruby_restored_xlsx/sc032d_３日目：みるく.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc032d_３日目：みるく.ss.xlsx
@@ -516,8 +516,8 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>We all read it once, but I guess it's possible she
-took it because she got interested……</t>
+          <t>We all did read it together once, but it's possible
+she took it because she was curious...</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -548,8 +548,9 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>She's honest and can't lie, so if she realizes she
-has it she'll probably return it.</t>
+          <t>Miru-chan is honest and can't lie, so if it's
+discovered that she has it, she'll probably return
+it.</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -579,8 +580,8 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>……For now, I came to the door in front of Miru-chan
-and Rin-chan's room.</t>
+          <t>…For now, I made it to the front of Miru-chan and
+Rin-chan's room.</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -595,7 +596,7 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>I wonder if they're in？</t>
+          <t>I wonder if Miru-chan is in?</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -610,7 +611,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>Knock knock…….</t>
+          <t>Knock knock...</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -640,7 +641,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>「Heeey, Miru-chaaan？」</t>
+          <t>「Hey, Miru-chan?」</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -670,7 +671,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>No answer again.</t>
+          <t>Still no answer.</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -685,7 +686,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Maybe neither Miru-chan nor Rin-chan are in the room？</t>
+          <t>Maybe Miru-chan and Rin-chan aren't in the room?</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -700,7 +701,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Hmm………………I know！</t>
+          <t>Hmm... I see!</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -715,7 +716,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>I slapped my palm.</t>
+          <t>I slapped my palm in realization.</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -730,8 +731,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>If she's going to read it, she'd do it secretly by
-herself.</t>
+          <t>If Miru-chan were going to look at it, she'd do it
+alone and in secret.</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -792,8 +793,9 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>I got cocky and made a bunch of guesses, but when it
-comes to where Miru-chan would be, I have no idea.</t>
+          <t>I got a bit carried away and made all sorts of
+guesses, but when it comes to where Miru-chan might
+be, I have no idea.</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -841,8 +843,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>That's why I'd rather meet only Miru-chan, if
-possible.</t>
+          <t>So, if possible, I'd like to meet Miru-chan alone.</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -962,7 +963,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>「Nn… fuu…」</t>
+          <t>「Mmm... phew...」</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1007,7 +1008,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>「Phew… nn… nngh…！」</t>
+          <t>"Phew... mmm... nngh...!"</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1052,7 +1053,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>……………huh？</t>
+          <t>……Huh？</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1067,8 +1068,8 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>On closer look, she’s pressing the buzzing brush head
-against her between her legs.</t>
+          <t>On closer look, she's pressing the vibrating brush
+head against the area between her legs.</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1083,7 +1084,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>……………what？!</t>
+          <t>……Huh?</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1098,8 +1099,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>…Seeing something so unexpected makes my mind go
-blank.</t>
+          <t>…At the sight of such an unexpected scene, my mind
+went completely blank.</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1114,8 +1115,8 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>She read a dirty book, learned what sex is like, got
-curious about it…</t>
+          <t>She read an erotic book, learned about sex, and
+became curious about it…</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1130,7 +1131,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>Up until that point I’d vaguely imagined those
+          <t>Up until then, I’d been vaguely imagining such
 things.</t>
         </is>
       </c>
@@ -1146,8 +1147,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>I even thought she might, out of curiosity… do
-something like that.</t>
+          <t>I even thought she might do it out of curiosity.</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1162,7 +1162,8 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>But for her to actually be doing it…！</t>
+          <t>But I can't believe Miru-chan is actually doing
+it...!</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1177,8 +1178,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>And on top of that, she’s using my electric
-toothbrush to stimulate her between her legs…</t>
+          <t>I can't believe she'd use my electric toothbrush to
+stimulate herself between her legs...</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1193,9 +1194,9 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>Come to think of it, you were just staring at my
-toothbrush before… Have you been interested since
-then…？</t>
+          <t>Come to think of it, Miru-chan was staring intently
+at my toothbrush earlier… Has she been interested
+since then…?</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1210,8 +1211,8 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Well, Miru-chan really comes up with some crazy
-ideas...！</t>
+          <t>Oh my, Miru-chan really comes up with some amazing
+ideas...!</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1241,7 +1242,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>「Nnh... Huff... N'ah...！」</t>
+          <t>「Mmm... huff... nngh...!」</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1256,7 +1257,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>And Miru-chan, holding her breath, has her shoulders
+          <t>Miru-chan, holding her breath, had her shoulders
 twitching.</t>
         </is>
       </c>
@@ -1272,8 +1273,8 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Her expression is tense, but not painfully so, and
-yet as if melting...</t>
+          <t>Her expression was tense, but not painfully so, and
+yet it looked as if she were melting...</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1288,7 +1289,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Oh... I think you’re probably already feeling it...</t>
+          <t>Oh... I'm probably feeling it already...</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1335,7 +1336,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>「Nn...nku, nn, n'uh...！」</t>
+          <t>"Mmm... mmph... mm... mmm...!"</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1350,8 +1351,8 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan doesn't notice me; she's lost in the
-stimulation from the electric toothbrush.</t>
+          <t>Miru-chan doesn't notice me; she's absorbed in the
+sensations from my electric toothbrush.</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1366,8 +1367,8 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>She presses the toothbrush head through her panties,
-and it looks like it feels good...</t>
+          <t>She's pressing the electric toothbrush head through
+her panties; it looks like she's enjoying it.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1397,7 +1398,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>「Nngh... nn... fuuuh...」</t>
+          <t>Nngh... nn... fuuuh...</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1428,8 +1429,9 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>I'm messing with myself down there with my toothbrush
-— I wonder if I'm feeling guilty about it？</t>
+          <t>She's using my toothbrush to stimulate herself
+between her legs — could she be feeling guilty about
+it?</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1460,7 +1462,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>But... it still feels good, right？</t>
+          <t>But... I might be feeling it...?</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1490,7 +1492,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>「Kufu... ugh... nn...! Nn!？!」</t>
+          <t>「Mmm... ugh... nn...! Nn!?」</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1505,7 +1507,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>...For a moment, Miru-chan's breath popped like that.</t>
+          <t>…Then Miru-chan's breath burst out for an instant.</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1520,8 +1522,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Did the toothbrush hit a really good spot by
-accident？</t>
+          <t>Did my toothbrush accidentally hit a good spot?</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1566,7 +1567,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>「Ah..................!!」</t>
+          <t>「Ah...!」</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1597,8 +1598,8 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Is this the first time she's becoming aware of
-feeling pleasure...？</t>
+          <t>Is this the first time she's realized what it means
+to feel...?</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1643,8 +1644,8 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Watching Miru-chan's toothbrush masturbation made my
-chest warm for some reason.</t>
+          <t>Watching Miru-chan masturbating with a toothbrush
+made my chest feel strangely warm.</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1659,7 +1660,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Is this how everyone grows up, I wonder...?</t>
+          <t>I wonder if this is how everyone grows up...</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1690,8 +1691,8 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>Yet honestly, watching her show interest in sexual
-things is turning me on...！</t>
+          <t>But, to be honest, watching her show interest in
+sexual things turns me on...!</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1736,7 +1737,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan's actions continued.</t>
+          <t>Miru-chan continued what she was doing.</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1751,9 +1752,9 @@
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>After a long sigh, she nodded as if steeling herself
-and pressed the head against her between her legs
-again.</t>
+          <t>After a long sigh, she nodded as if she'd made up her
+mind, and pressed the toothbrush head against the
+area between her legs again.</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1783,7 +1784,7 @@
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>「Umm... nn？ Nn~... fua!？!」</t>
+          <t>「Umm... Nn? Nn~... fua!?」</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1799,8 +1800,8 @@
       <c r="B87" s="1" t="inlineStr">
         <is>
           <t>She seemed to be searching for the spot she'd felt
-earlier, but when it actually hit, she couldn't help
-making a sound.</t>
+earlier, but when the head actually hit it, she
+couldn't help making a sound.</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1815,8 +1816,8 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>Then she looked surprised again, eyes round, staring
-down at her crotch.</t>
+          <t>Then she looked surprised again, her eyes round as
+she peered down between her legs.</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1831,8 +1832,8 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>She seems to be gradually figuring out the good
-spots, but it's still a mysterious feeling to her.</t>
+          <t>Miru-chan seems to be gradually figuring out the good
+spots, but it probably still feels strange to her.</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1862,7 +1863,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nn~？ Fuu... hya'n！？」</t>
+          <t>「Nn... nn~? Fuu... hya!?」</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1877,8 +1878,8 @@
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>She kept pressing the good spot and startling
-herself.</t>
+          <t>She pressed it against the good spot again and
+startled herself.</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,8 +1909,8 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>Seeing Miru-chan purely and sexually excited made my
-chest warm again.</t>
+          <t>Watching Miru-chan genuinely sexually aroused made my
+chest heat up again.</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1954,7 +1955,7 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>「A-again...nn, uhh...nnn！？」</t>
+          <t>「A-again... nn... nnn!?」</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1969,8 +1970,8 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan probes the spot again and again like she's
-experimenting, and each time she gets startled.</t>
+          <t>Miru-chan keeps feeling around for the spot as if
+testing it, and is startled each time.</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2002,8 +2003,8 @@
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>So she keeps doing it, and she keeps getting
-surprised.</t>
+          <t>So she does it over and over, and is surprised each
+time.</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2018,7 +2019,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Ugh... I want to teach her.</t>
+          <t>Ugh... I want to teach her how.</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2033,7 +2034,7 @@
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>I want to take her hands and guide her through it！</t>
+          <t>I want to teach her step by step!</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2063,7 +2064,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>「Fua...nn, nn...ah！？」</t>
+          <t>「fua... nn, nnn... ah!?」</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2078,7 +2079,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Miru-chan repeats the same thing again.</t>
+          <t>Miru-chan repeats the same thing.</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2110,7 +2111,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>I cheered Miru-chan on in my heart.</t>
+          <t>I silently cheered for Miru-chan.</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2125,8 +2126,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>If you try, the more you try the better it'll
-feel...！</t>
+          <t>The more you try, the better it'll feel...!</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>「Nn...hh, huu, huu...」</t>
+          <t>「Nn...! Fuu, fuu...」</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2203,7 +2203,7 @@
       <c r="B113" s="1" t="inlineStr">
         <is>
           <t>But since she's starting to realize it feels good,
-she ends up moving the toothbrush toward between her
+she ends up moving the toothbrush to between her
 legs.</t>
         </is>
       </c>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>「...fu, u, uuh...ha！ Ah！」</t>
+          <t>"...fuh... uh... uuh... ha! Ah!"</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2264,8 +2264,9 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>She seemed to press it on consciously, and being
-startled and flinching happened at the same time.</t>
+          <t>Miru-chan seemed to press it on deliberately, and she
+was startled and gave a little shudder at the same
+time.</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2311,7 +2312,7 @@
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>「...huh...huh...huh！」</t>
+          <t>「...fuu... fuu... fuu...!」</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2357,7 +2358,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Did she think it was enough already？</t>
+          <t>I wonder if she thought that was enough already?</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2387,7 +2388,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>「...u, uuh... uuh~...！」</t>
+          <t>「...uh, uuh... uuh~...!」</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2417,7 +2418,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>Did she start feeling ashamed of what she was doing？</t>
+          <t>Did she start to feel ashamed of what she was doing?</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2432,9 +2433,8 @@
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>No sooner had I thought that, Miru-chan began
-pressing the toothbrush against her between (my/her)
-legs again.</t>
+          <t>Just then, Miru-chan again began pressing the
+toothbrush between her legs.</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nk！ Nn！ N, k...！」</t>
+          <t>「Nn... nku! Nn! n, ku...!」</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2479,9 +2479,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>With the toothbrush against her between (my/her)
-legs, Miru-chan trembled as she desperately stifled
-her voice.</t>
+          <t>With the toothbrush pressed between her legs,
+Miru-chan trembled, desperately stifling her voice.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2496,7 +2495,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>This is definitely on purpose...！</t>
+          <t>She's definitely doing this on purpose...!</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2526,7 +2525,7 @@
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>「fu, guhh… u, uuuuu… k… nnaah！？」</t>
+          <t>「Fuh... guh... uuu... k... nnaah!?」</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2556,8 +2555,8 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>It seemed like she held back, but the stimulation was
-stronger.</t>
+          <t>She seemed to try to hold back, but the stimulation
+was stronger.</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2587,7 +2586,7 @@
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>「Ah！  ………uu…」</t>
+          <t>「Ah! ...uuh...」</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2602,7 +2601,7 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>And then, suddenly, she started acting all nervous.</t>
+          <t>Then, unlike before, she began to act nervously.</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2677,9 +2676,9 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>...Miru-chan stared off for a bit, then suddenly
-flustered, headed for the sink and started rinsing
-her toothbrush with water.</t>
+          <t>Miru-chan had been spacing out for a while, but
+suddenly she hurried to the sink and began rinsing
+her toothbrush under the tap.</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2709,7 +2708,7 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>「...haah」</t>
+          <t>「...haa!」</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2739,9 +2738,8 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>She’s probably feeling regret and guilt about what
-she’s done up till now, and a kind of relief that
-nobody saw it.</t>
+          <t>She's probably feeling regret and guilt about what
+she's done so far, and relief that nobody saw her.</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2786,8 +2784,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Holding my throbbing chest and crotch, I watched
-Miru-chan put the toothbrush back where it belonged.</t>
+          <t>As I held my tingling chest and crotch, Miru-chan put
+the toothbrush back in its original place.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2832,8 +2830,8 @@
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>…Oh no. She might already be coming out of the
-bathroom.</t>
+          <t>This is bad. She might already be coming out of the
+washroom.</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2864,7 +2862,8 @@
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Then when I got to the stairs, I ran up them...！</t>
+          <t>Then, when Miru-chan reached the stairs, she dashed
+up the stairs...!</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2894,7 +2893,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>「Hah, huu~~~...！」</t>
+          <t>「Hah... huuu~~~...！」</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2909,7 +2908,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>I went back to my room and let out a big sigh.</t>
+          <t>She went back to her room and let out a big sigh.</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2971,8 +2970,8 @@
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>If possible, I want to teach you properly, even more
-deeply.</t>
+          <t>If possible, I'd like to teach Miru-chan properly,
+going even deeper.</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2987,7 +2986,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>It's for her own good to learn things on her own, you
+          <t>But it's better for her to learn on her own, you
 know.</t>
         </is>
       </c>
@@ -3003,7 +3002,7 @@
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>...But again, we couldn't retrieve Comic RO.</t>
+          <t>...But again, I couldn't retrieve Comic RO.</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3033,7 +3032,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>I'll pick it up tomorrow...</t>
+          <t>I'll pick it up again tomorrow...</t>
         </is>
       </c>
       <c r="C167" t="n">
